--- a/4_Documentation/codebook_clean.xlsx
+++ b/4_Documentation/codebook_clean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/varvarailyina/hertie/ML/US_conflict_forecasting/4_Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3503CF6-D0DC-3443-BDBE-17CEEDBF7D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6894ABAA-8C76-5F45-8741-F8A7B454F65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40" yWindow="760" windowWidth="23300" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="760" windowWidth="23300" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="251">
   <si>
     <t>var_name</t>
   </si>
@@ -772,6 +772,9 @@
   </si>
   <si>
     <t>index on the right side</t>
+  </si>
+  <si>
+    <t>important</t>
   </si>
 </sst>
 </file>
@@ -820,19 +823,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1139,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
@@ -1149,7 +1146,7 @@
     <col min="6" max="6" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1168,8 +1165,11 @@
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G1" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1188,8 +1188,11 @@
       <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1211,11 @@
       <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1226,8 +1232,11 @@
       <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1244,8 +1253,11 @@
       <c r="F5" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1274,11 @@
       <c r="F6" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -1280,8 +1295,11 @@
       <c r="F7" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -1298,8 +1316,11 @@
       <c r="F8" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1316,8 +1337,11 @@
       <c r="F9" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1336,8 +1360,11 @@
       <c r="F10" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -1356,8 +1383,11 @@
       <c r="F11" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
@@ -1376,8 +1406,11 @@
       <c r="F12" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
@@ -1396,15 +1429,18 @@
       <c r="F13" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="3" t="s">
         <v>172</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -1416,15 +1452,18 @@
       <c r="F14" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="3" t="s">
         <v>172</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -1436,8 +1475,11 @@
       <c r="F15" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>20</v>
       </c>
@@ -1456,8 +1498,11 @@
       <c r="F16" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
@@ -1476,8 +1521,11 @@
       <c r="F17" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
@@ -1496,8 +1544,11 @@
       <c r="F18" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
@@ -1516,8 +1567,11 @@
       <c r="F19" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
@@ -1536,8 +1590,11 @@
       <c r="F20" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>25</v>
       </c>
@@ -1556,15 +1613,18 @@
       <c r="F21" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="1" t="s">
         <v>172</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -1576,8 +1636,11 @@
       <c r="F22" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>27</v>
       </c>
@@ -1596,8 +1659,11 @@
       <c r="F23" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>29</v>
       </c>
@@ -1616,8 +1682,11 @@
       <c r="F24" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>30</v>
       </c>
@@ -1636,8 +1705,11 @@
       <c r="F25" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>31</v>
       </c>
@@ -1656,8 +1728,11 @@
       <c r="F26" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
@@ -1676,8 +1751,11 @@
       <c r="F27" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
@@ -1696,8 +1774,11 @@
       <c r="F28" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
@@ -1716,8 +1797,11 @@
       <c r="F29" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>36</v>
       </c>
@@ -1736,8 +1820,11 @@
       <c r="F30" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -1756,8 +1843,11 @@
       <c r="F31" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
@@ -1776,8 +1866,11 @@
       <c r="F32" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="G32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
@@ -1796,8 +1889,11 @@
       <c r="F33" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="G33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
@@ -1816,8 +1912,11 @@
       <c r="F34" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="G34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
@@ -1836,8 +1935,11 @@
       <c r="F35" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="G35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>42</v>
       </c>
@@ -1856,8 +1958,11 @@
       <c r="F36" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="G36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>43</v>
       </c>
@@ -1876,8 +1981,11 @@
       <c r="F37" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="G37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>44</v>
       </c>
@@ -1896,8 +2004,11 @@
       <c r="F38" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="G38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>45</v>
       </c>
@@ -1916,8 +2027,11 @@
       <c r="F39" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>46</v>
       </c>
@@ -1936,8 +2050,11 @@
       <c r="F40" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="G40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>47</v>
       </c>
@@ -1956,8 +2073,11 @@
       <c r="F41" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>48</v>
       </c>
@@ -1976,8 +2096,11 @@
       <c r="F42" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="G42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>49</v>
       </c>
@@ -1996,8 +2119,11 @@
       <c r="F43" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="G43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>50</v>
       </c>
@@ -2016,11 +2142,14 @@
       <c r="F44" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
@@ -2039,12 +2168,15 @@
       <c r="F45" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="1" t="s">
         <v>209</v>
       </c>
       <c r="C46" s="1" t="s">
@@ -2059,12 +2191,15 @@
       <c r="F46" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="G46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="1" t="s">
         <v>210</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -2079,8 +2214,11 @@
       <c r="F47" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+      <c r="G47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>54</v>
       </c>
@@ -2099,8 +2237,11 @@
       <c r="F48" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>55</v>
       </c>
@@ -2119,8 +2260,11 @@
       <c r="F49" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>56</v>
       </c>
@@ -2139,8 +2283,11 @@
       <c r="F50" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>57</v>
       </c>
@@ -2159,15 +2306,18 @@
       <c r="F51" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+      <c r="G51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="48" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="1" t="s">
         <v>218</v>
       </c>
       <c r="D52" s="1" t="s">
@@ -2179,8 +2329,11 @@
       <c r="F52" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>59</v>
       </c>
@@ -2199,8 +2352,11 @@
       <c r="F53" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>60</v>
       </c>
@@ -2219,8 +2375,11 @@
       <c r="F54" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>61</v>
       </c>
@@ -2239,8 +2398,11 @@
       <c r="F55" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>62</v>
       </c>
@@ -2259,8 +2421,11 @@
       <c r="F56" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>64</v>
       </c>
@@ -2279,8 +2444,11 @@
       <c r="F57" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>65</v>
       </c>
@@ -2299,8 +2467,11 @@
       <c r="F58" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>67</v>
       </c>
@@ -2319,8 +2490,11 @@
       <c r="F59" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>68</v>
       </c>
@@ -2339,8 +2513,11 @@
       <c r="F60" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>70</v>
       </c>
@@ -2359,8 +2536,11 @@
       <c r="F61" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>71</v>
       </c>
@@ -2379,8 +2559,11 @@
       <c r="F62" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>72</v>
       </c>
@@ -2399,8 +2582,11 @@
       <c r="F63" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>73</v>
       </c>
@@ -2419,8 +2605,11 @@
       <c r="F64" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>74</v>
       </c>
@@ -2439,8 +2628,11 @@
       <c r="F65" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>75</v>
       </c>
@@ -2459,8 +2651,11 @@
       <c r="F66" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>76</v>
       </c>
@@ -2479,8 +2674,11 @@
       <c r="F67" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>77</v>
       </c>
@@ -2499,8 +2697,11 @@
       <c r="F68" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>78</v>
       </c>
@@ -2517,8 +2718,11 @@
       <c r="F69" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>80</v>
       </c>
@@ -2535,8 +2739,11 @@
       <c r="F70" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>81</v>
       </c>
@@ -2553,8 +2760,11 @@
       <c r="F71" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>82</v>
       </c>
@@ -2571,8 +2781,11 @@
       <c r="F72" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>83</v>
       </c>
@@ -2589,8 +2802,11 @@
       <c r="F73" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>84</v>
       </c>
@@ -2607,8 +2823,11 @@
       <c r="F74" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>85</v>
       </c>
@@ -2625,8 +2844,11 @@
       <c r="F75" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>86</v>
       </c>
@@ -2643,8 +2865,11 @@
       <c r="F76" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>87</v>
       </c>
@@ -2661,8 +2886,11 @@
       <c r="F77" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>88</v>
       </c>
@@ -2681,8 +2909,11 @@
       <c r="F78" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>89</v>
       </c>
@@ -2701,8 +2932,11 @@
       <c r="F79" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>90</v>
       </c>
@@ -2721,8 +2955,11 @@
       <c r="F80" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>91</v>
       </c>
@@ -2741,8 +2978,11 @@
       <c r="F81" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>92</v>
       </c>
@@ -2761,8 +3001,11 @@
       <c r="F82" s="1" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>1</v>
       </c>
@@ -2781,8 +3024,11 @@
       <c r="F83" s="1" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>94</v>
       </c>
@@ -2801,12 +3047,15 @@
       <c r="F84" s="1" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="1" t="s">
         <v>133</v>
       </c>
       <c r="C85" s="1" t="s">
@@ -2821,12 +3070,15 @@
       <c r="F85" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="1" t="s">
         <v>134</v>
       </c>
       <c r="C86" s="1" t="s">
@@ -2841,12 +3093,15 @@
       <c r="F86" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="1" t="s">
         <v>135</v>
       </c>
       <c r="C87" s="1" t="s">
@@ -2861,12 +3116,15 @@
       <c r="F87" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="1" t="s">
         <v>136</v>
       </c>
       <c r="C88" s="1" t="s">
@@ -2881,12 +3139,15 @@
       <c r="F88" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="1" t="s">
         <v>137</v>
       </c>
       <c r="C89" s="1" t="s">
@@ -2901,12 +3162,15 @@
       <c r="F89" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="1" t="s">
         <v>138</v>
       </c>
       <c r="C90" s="1" t="s">
@@ -2921,12 +3185,15 @@
       <c r="F90" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="1" t="s">
         <v>139</v>
       </c>
       <c r="C91" s="1" t="s">
@@ -2941,12 +3208,15 @@
       <c r="F91" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="1" t="s">
         <v>140</v>
       </c>
       <c r="C92" s="1" t="s">
@@ -2961,12 +3231,15 @@
       <c r="F92" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="1" t="s">
         <v>141</v>
       </c>
       <c r="C93" s="1" t="s">
@@ -2981,12 +3254,15 @@
       <c r="F93" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="1" t="s">
         <v>142</v>
       </c>
       <c r="C94" s="1" t="s">
@@ -3001,12 +3277,15 @@
       <c r="F94" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="1" t="s">
         <v>143</v>
       </c>
       <c r="C95" s="1" t="s">
@@ -3021,12 +3300,15 @@
       <c r="F95" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="1" t="s">
         <v>144</v>
       </c>
       <c r="C96" s="1" t="s">
@@ -3041,12 +3323,15 @@
       <c r="F96" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="1" t="s">
         <v>145</v>
       </c>
       <c r="C97" s="1" t="s">
@@ -3061,12 +3346,15 @@
       <c r="F97" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="1" t="s">
         <v>146</v>
       </c>
       <c r="C98" s="1" t="s">
@@ -3081,12 +3369,15 @@
       <c r="F98" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="1" t="s">
         <v>147</v>
       </c>
       <c r="C99" s="1" t="s">
@@ -3101,8 +3392,11 @@
       <c r="F99" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>111</v>
       </c>
@@ -3121,8 +3415,11 @@
       <c r="F100" s="1" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>113</v>
       </c>
@@ -3141,8 +3438,11 @@
       <c r="F101" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>115</v>
       </c>
@@ -3161,8 +3461,11 @@
       <c r="F102" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>116</v>
       </c>
@@ -3181,8 +3484,11 @@
       <c r="F103" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>117</v>
       </c>
@@ -3201,12 +3507,15 @@
       <c r="F104" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B105" s="1" t="s">
         <v>155</v>
       </c>
       <c r="C105" s="1" t="s">
@@ -3221,12 +3530,15 @@
       <c r="F105" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" s="1" t="s">
         <v>154</v>
       </c>
       <c r="C106" s="1" t="s">
@@ -3241,8 +3553,11 @@
       <c r="F106" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>120</v>
       </c>
@@ -3261,8 +3576,11 @@
       <c r="F107" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>121</v>
       </c>
@@ -3281,8 +3599,11 @@
       <c r="F108" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>122</v>
       </c>
@@ -3301,8 +3622,11 @@
       <c r="F109" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>123</v>
       </c>
@@ -3321,8 +3645,11 @@
       <c r="F110" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>124</v>
       </c>
@@ -3341,8 +3668,11 @@
       <c r="F111" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>125</v>
       </c>
@@ -3361,8 +3691,11 @@
       <c r="F112" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>131</v>
       </c>
@@ -3381,8 +3714,11 @@
       <c r="F113" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>126</v>
       </c>
@@ -3401,8 +3737,11 @@
       <c r="F114" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>127</v>
       </c>
@@ -3421,8 +3760,11 @@
       <c r="F115" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>128</v>
       </c>
@@ -3441,8 +3783,11 @@
       <c r="F116" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="G116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>129</v>
       </c>
@@ -3461,8 +3806,11 @@
       <c r="F117" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="G117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>130</v>
       </c>
@@ -3480,6 +3828,9 @@
       </c>
       <c r="F118" s="1" t="s">
         <v>114</v>
+      </c>
+      <c r="G118">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
